--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-del-libertador-general-bernardo-o-higgins.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-del-libertador-general-bernardo-o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>591-86-CM26</t>
+          <t>2675-30-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.376.088-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1718926.68</v>
+        <v>18937.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3954-31-CM26</t>
+          <t>2677-28-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+          <t>Rayen Salud SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.286.397-9</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>223123.85</v>
+        <v>60481.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>591-293-CM26</t>
+          <t>1620-50-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73717.23</v>
+        <v>7971.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3729-93-CM26</t>
+          <t>3598-171-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.286.397-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,982 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>205644.03</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3810-756-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.091.200-7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MEETCARD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.437.288-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>19985.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3598-430-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.091.300-3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>23779.96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1126920-151-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>62.000.790-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE COLCHAGUA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Andes Digital</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.975.787-2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>6891.84</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>557639-793-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>71.014.200-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Rayen Salud SpA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1108739.21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1529-270-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.602.140-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>43420.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1743-384-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.091.100-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>175880.58</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>591-7471-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CLARO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.799.250-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1564746.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1398-2161-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.800-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAMPIT SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.782.984-1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>29356.12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1398-2284-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.606.800-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PRAGMA INFORMATICA S.A.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>36105.67</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>557639-1899-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>71.014.200-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Rayen Salud SpA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.917.240-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>56223.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2401-934-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.080.100-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SolNet SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.723.130-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>34724.27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3181-488-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.080.200-7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>8094.17</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>591-86-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>APIUX TECNOLOGIA SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.516.485-0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1718926.68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3954-31-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.091.500-6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>223123.85</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>591-293-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>61.603.000-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FONDO NACIONAL DE SALUD</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>73717.23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3729-93-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.090.300-8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
         <v>8273.450000000001</v>
       </c>
     </row>
